--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="94">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMTraitement vers le profil CDA FRCDATraitement, puis vers le profil FHIR FRMedicationAdministrationDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMMedicationAdministration vers le profil CDA FRCDATraitement (Groupe 1), et vers le profil FHIR FRMedicationAdministrationDocument (Groupe 2).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-administration</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-traitement</t>
   </si>
   <si>
-    <t>FRLMTraitement</t>
+    <t>FRLMMedicationAdministration</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,106 +118,124 @@
     <t>FRCDATraitement</t>
   </si>
   <si>
-    <t>FRLMTraitement.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.id</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.code</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.code</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.note</t>
+    <t>FRLMMedicationAdministration.medication</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.consumable</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime[not(@operator='A')]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime[@operator='A']</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.reason[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.entryRelationship:frTraitement.entryRelationship:frReferenceInterne</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.renderedDosageInstruction</t>
   </si>
   <si>
     <t>FRCDATraitement.text</t>
   </si>
   <si>
-    <t>FRLMTraitement.status</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.occurancePeriod</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime[not(@operator='A')]</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.occuranceDateTim</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime[@operator='A']</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.route</t>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.note</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.doseQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.doseAndRate.rate[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.rateQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.numberOfTimes</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime.frequency</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.period</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime.period</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.additionalInstructions</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.dateOfAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.conditionOfAdministration</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.precondition</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.date[x]</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.eventTime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.approachSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.routeOfAdministration</t>
   </si>
   <si>
     <t>FRCDATraitement.routeCode</t>
   </si>
   <si>
-    <t>FRLMTraitement.dosage.site</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.approachSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.dose</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.doseQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.rate[x]</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.rateQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.doseMaximale</t>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerPeriod.quantity</t>
   </si>
   <si>
     <t>FRCDATraitement.maxDoseQuantity</t>
   </si>
   <si>
-    <t>FRLMTraitement.medicament</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.consumable</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.reason</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frReferenceInterne</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.prescription</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frPrescription</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.subordinateTreatment</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frTraitementSubordonne</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.instructionsPatient</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.precondition</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.precondition</t>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerPeriod.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxLifetimeDose</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.note</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document</t>
@@ -226,16 +244,7 @@
     <t>FRMedicationAdministrationDocument</t>
   </si>
   <si>
-    <t>FRMedicationAdministrationDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.category</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.category.text</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.status</t>
+    <t>FRMedicationAdministrationDocument.medication:FRMedicationDocument</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.effectivePeriod</t>
@@ -244,34 +253,46 @@
     <t>FRMedicationAdministrationDocument.extension:medicationAdministration-occurence-r5</t>
   </si>
   <si>
+    <t>FRMedicationAdministrationDocument.reasonReference</t>
+  </si>
+  <si>
+    <t>FRMedicationAdministrationDocument.reasonCode</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage</t>
+  </si>
+  <si>
+    <t>FRMedicationAdministrationDocument.dosage</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.renderedDosageInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationAdministrationDocument.dosage.text</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.routeOfAdministration</t>
+  </si>
+  <si>
     <t>FRMedicationAdministrationDocument.dosage.route</t>
   </si>
   <si>
-    <t>FRMedicationAdministrationDocument.dosage.site</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.dose[x]</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.dosage.dose</t>
   </si>
   <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.rate[x]</t>
+  </si>
+  <si>
     <t>FRMedicationAdministrationDocument.dosage.rate[x]</t>
   </si>
   <si>
-    <t>FRMedicationAdministrationDocument.dosage.rateRatio</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.medication:FRMedicationDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.reasonReference</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.request</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.medication:FRMedicationsCombinaisonDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage.text</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.sequence</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.extension:FRMedicationAdministrationSequenceExtension</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.note</t>
@@ -526,7 +547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -604,198 +625,315 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E29" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -804,7 +942,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -826,7 +964,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -835,7 +973,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -843,237 +981,172 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="E20" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="91">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-administration</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-medication-administration|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-traitement</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-traitement|0.1.0</t>
   </si>
   <si>
     <t>FRLMMedicationAdministration</t>
@@ -139,106 +139,106 @@
     <t>FRCDATraitement.entryRelationship:frTraitement.entryRelationship:frReferenceInterne</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.renderedDosageInstruction</t>
+    <t>FRLMMedicationAdministration.dosage.renderedDosageInstruction</t>
   </si>
   <si>
     <t>FRCDATraitement.text</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.note</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.note</t>
   </si>
   <si>
     <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.doseAndRate.dose[x]</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.dose[x]</t>
   </si>
   <si>
     <t>FRCDATraitement.doseQuantity</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.doseAndRate.rate[x]</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.rate[x]</t>
   </si>
   <si>
     <t>FRCDATraitement.rateQuantity</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency</t>
   </si>
   <si>
     <t>FRCDATraitement.effectiveTime</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.numberOfTimes</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.numberOfTimes</t>
   </si>
   <si>
     <t>FRCDATraitement.effectiveTime.frequency</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.period</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.period</t>
   </si>
   <si>
     <t>FRCDATraitement.effectiveTime.period</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.dayOfWeek</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.timeOfDay</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.additionalInstructions</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.dateOfAdministration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.conditionOfAdministration</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.additionalInstructions</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.dateOfAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.conditionOfAdministration</t>
   </si>
   <si>
     <t>FRCDATraitement.precondition</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.date[x]</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.duration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.eventTime</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.bodySite</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.date[x]</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.eventTime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.bodySite</t>
   </si>
   <si>
     <t>FRCDATraitement.approachSiteCode</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.routeOfAdministration</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.routeOfAdministration</t>
   </si>
   <si>
     <t>FRCDATraitement.routeCode</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerPeriod.quantity</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxDosePerPeriod.quantity</t>
   </si>
   <si>
     <t>FRCDATraitement.maxDoseQuantity</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerPeriod.duration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerAdministration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxLifetimeDose</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxDosePerPeriod.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxLifetimeDose</t>
   </si>
   <si>
     <t>FRLMMedicationAdministration.note</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument</t>
@@ -265,25 +265,16 @@
     <t>FRMedicationAdministrationDocument.dosage</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosage.renderedDosageInstruction</t>
-  </si>
-  <si>
     <t>FRMedicationAdministrationDocument.dosage.text</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.routeOfAdministration</t>
+    <t>FRMedicationAdministrationDocument.dosage.site</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.dosage.route</t>
   </si>
   <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.dose[x]</t>
-  </si>
-  <si>
     <t>FRMedicationAdministrationDocument.dosage.dose</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.rate[x]</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.dosage.rate[x]</t>
@@ -942,7 +933,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1072,81 +1063,94 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E16" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -9,12 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
+    <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
+    <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +39,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRMedicationAdministrationLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +108,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-medication-administration|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,178 +123,178 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>SubstanceAdministration</t>
+  </si>
+  <si>
     <t>FRCDATraitement</t>
   </si>
   <si>
     <t>FRLMMedicationAdministration.medication</t>
   </si>
   <si>
-    <t>FRCDATraitement.consumable</t>
+    <t>SubstanceAdministration.consumable</t>
   </si>
   <si>
     <t>FRLMMedicationAdministration.occurrence[x]</t>
   </si>
   <si>
-    <t>FRCDATraitement.effectiveTime[not(@operator='A')]</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime[@operator='A']</t>
+    <t>SubstanceAdministration.effectiveTime</t>
   </si>
   <si>
     <t>FRLMMedicationAdministration.reason[x]</t>
   </si>
   <si>
-    <t>FRCDATraitement.entryRelationship:frTraitement.entryRelationship:frReferenceInterne</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.renderedDosageInstruction</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.text</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.note</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.dose[x]</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.doseQuantity</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.rate[x]</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.rateQuantity</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.numberOfTimes</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime.frequency</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.period</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime.period</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.dayOfWeek</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.timeOfDay</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.frequency.additionalInstructions</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.dateOfAdministration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.conditionOfAdministration</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.precondition</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.date[x]</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.duration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.eventTime</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.bodySite</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.approachSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.routeOfAdministration</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.routeCode</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxDosePerPeriod.quantity</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.maxDoseQuantity</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxDosePerPeriod.duration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxDosePerAdministration</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.maxLifetimeDose</t>
+    <t>SubstanceAdministration.entryRelationship:frReferenceInterne</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.text</t>
   </si>
   <si>
     <t>FRLMMedicationAdministration.note</t>
   </si>
   <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDosageInstructions|0.1.0</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.renderedDosageInstruction</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.note</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.entryRelationship:frInstructionsAuPatient</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.doseQuantity</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.doseAndRate.rate[x]</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.rateQuantity</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.frequency</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.effectiveTime:effectiveTimeFrequence</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.frequency.numberOfTimes</t>
+  </si>
+  <si>
+    <t>source-is-narrower-than-target</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.frequency.period</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.frequency.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.frequency.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.frequency.additionalInstructions</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.conditionOfAdministration</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.precondition</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.date[x]</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.effectiveTime:effectiveTimeDuree</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.eventTime</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.bodySite</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.approachSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.routeOfAdministration</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.routeCode</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.maxDosePerPeriod.quantity</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.maxDoseQuantity.numerator</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.maxDosePerPeriod.duration</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.maxDoseQuantity.denominator</t>
+  </si>
+  <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0</t>
   </si>
   <si>
+    <t>MedicationAdministration</t>
+  </si>
+  <si>
     <t>FRMedicationAdministrationDocument</t>
   </si>
   <si>
-    <t>FRMedicationAdministrationDocument.medication:FRMedicationDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.effectivePeriod</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.extension:medicationAdministration-occurence-r5</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.reasonReference</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.reasonCode</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage.text</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage.site</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage.route</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage.dose</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage.rate[x]</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.dosageDetails.sequence</t>
-  </si>
-  <si>
-    <t>FRLMMedicationAdministration.dosage.extension:FRMedicationAdministrationSequenceExtension</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.note</t>
+    <t>MedicationAdministration.medication[x]</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.effective[x]</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.extension:occurenceR5</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.reasonReference</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.reasonCode</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.note</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.text</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.site</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.route</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.dose</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.rate[x]</t>
+  </si>
+  <si>
+    <t>FRLMDosageInstructions.dosageDetails.sequence</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.dosage.extension:sequence</t>
   </si>
 </sst>
 </file>
@@ -455,79 +463,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -538,393 +550,122 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="E29" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -933,224 +674,535 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
